--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/73.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/73.xlsx
@@ -426,13 +426,13 @@
         <v>-11.43058417137384</v>
       </c>
       <c r="E2">
-        <v>-5.937877578259212</v>
+        <v>-4.773951074911746</v>
       </c>
       <c r="F2">
-        <v>-5.113156755113055</v>
+        <v>-5.064046993638086</v>
       </c>
       <c r="G2">
-        <v>-7.329846923713276</v>
+        <v>-6.996018132624249</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.27055505620693</v>
       </c>
       <c r="E3">
-        <v>-6.886891762150658</v>
+        <v>-5.66986437258925</v>
       </c>
       <c r="F3">
-        <v>-4.929005711266308</v>
+        <v>-5.264709884924835</v>
       </c>
       <c r="G3">
-        <v>-6.966607246053363</v>
+        <v>-7.04088926686353</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.14538322473894</v>
       </c>
       <c r="E4">
-        <v>-7.068429228170148</v>
+        <v>-6.141595509968271</v>
       </c>
       <c r="F4">
-        <v>-5.458764889439453</v>
+        <v>-5.306659238570005</v>
       </c>
       <c r="G4">
-        <v>-6.991131767408284</v>
+        <v>-7.375194776510213</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.07223956463531</v>
       </c>
       <c r="E5">
-        <v>-8.069140471333158</v>
+        <v>-6.913659572009998</v>
       </c>
       <c r="F5">
-        <v>-5.24876215568614</v>
+        <v>-5.335731620938657</v>
       </c>
       <c r="G5">
-        <v>-6.876239284467878</v>
+        <v>-7.250532873683417</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.04276028098245</v>
       </c>
       <c r="E6">
-        <v>-9.491362075130127</v>
+        <v>-7.594289215362853</v>
       </c>
       <c r="F6">
-        <v>-5.078582356455009</v>
+        <v>-5.053838193765985</v>
       </c>
       <c r="G6">
-        <v>-6.715416292715623</v>
+        <v>-7.1014391447768</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.0509245839042</v>
       </c>
       <c r="E7">
-        <v>-9.438614409888782</v>
+        <v>-9.262905089917165</v>
       </c>
       <c r="F7">
-        <v>-5.361386159403358</v>
+        <v>-5.184101452958416</v>
       </c>
       <c r="G7">
-        <v>-6.552746016552454</v>
+        <v>-7.088465116808396</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.07811691213469</v>
       </c>
       <c r="E8">
-        <v>-11.18296901222138</v>
+        <v>-10.0663831761501</v>
       </c>
       <c r="F8">
-        <v>-5.012195336059851</v>
+        <v>-5.005835131141157</v>
       </c>
       <c r="G8">
-        <v>-6.802635925493261</v>
+        <v>-6.900671110547699</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.1105486099105</v>
       </c>
       <c r="E9">
-        <v>-11.2829939461028</v>
+        <v>-9.868099413250247</v>
       </c>
       <c r="F9">
-        <v>-5.015995885703895</v>
+        <v>-4.743521824268456</v>
       </c>
       <c r="G9">
-        <v>-6.353742503095785</v>
+        <v>-6.601450762526212</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.12682343429163</v>
       </c>
       <c r="E10">
-        <v>-11.67131059226054</v>
+        <v>-10.8413228191867</v>
       </c>
       <c r="F10">
-        <v>-4.739785887281831</v>
+        <v>-5.148035164607928</v>
       </c>
       <c r="G10">
-        <v>-6.764339534694972</v>
+        <v>-6.000424530417067</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.11338784869709</v>
       </c>
       <c r="E11">
-        <v>-12.45388977094807</v>
+        <v>-12.02503875394768</v>
       </c>
       <c r="F11">
-        <v>-4.680164143465337</v>
+        <v>-4.608949397846663</v>
       </c>
       <c r="G11">
-        <v>-5.995336221923208</v>
+        <v>-6.05923637192222</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.05963920902151</v>
       </c>
       <c r="E12">
-        <v>-13.98638877377983</v>
+        <v>-13.27180916079147</v>
       </c>
       <c r="F12">
-        <v>-4.35670158328538</v>
+        <v>-4.814087958210738</v>
       </c>
       <c r="G12">
-        <v>-5.575161782078909</v>
+        <v>-6.043498038428525</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.95713960409626</v>
       </c>
       <c r="E13">
-        <v>-14.21928819199432</v>
+        <v>-14.31481182271212</v>
       </c>
       <c r="F13">
-        <v>-4.311130607355171</v>
+        <v>-4.330723981533588</v>
       </c>
       <c r="G13">
-        <v>-5.223426250167963</v>
+        <v>-5.240942346616246</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.81070065204598</v>
       </c>
       <c r="E14">
-        <v>-15.06703664012624</v>
+        <v>-14.39228495603534</v>
       </c>
       <c r="F14">
-        <v>-4.168846908780717</v>
+        <v>-4.223673233702405</v>
       </c>
       <c r="G14">
-        <v>-5.250758114140186</v>
+        <v>-4.412796137785402</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.62272497195067</v>
       </c>
       <c r="E15">
-        <v>-16.60682648611034</v>
+        <v>-16.41414897403198</v>
       </c>
       <c r="F15">
-        <v>-4.205889013931702</v>
+        <v>-4.289652697335385</v>
       </c>
       <c r="G15">
-        <v>-4.763998671864525</v>
+        <v>-4.577287213995169</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.40575078420162</v>
       </c>
       <c r="E16">
-        <v>-17.2438876810354</v>
+        <v>-17.20230723269697</v>
       </c>
       <c r="F16">
-        <v>-3.678661326541512</v>
+        <v>-3.892644365665277</v>
       </c>
       <c r="G16">
-        <v>-4.163872908142062</v>
+        <v>-3.390234831615318</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.17174210997979</v>
       </c>
       <c r="E17">
-        <v>-18.86250467407103</v>
+        <v>-17.50263110041166</v>
       </c>
       <c r="F17">
-        <v>-3.647993508555069</v>
+        <v>-3.643881492767572</v>
       </c>
       <c r="G17">
-        <v>-2.98595101035952</v>
+        <v>-3.399414974395717</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.937858623565155</v>
       </c>
       <c r="E18">
-        <v>-18.88970268896109</v>
+        <v>-18.90589651201253</v>
       </c>
       <c r="F18">
-        <v>-3.051344490973266</v>
+        <v>-3.383871875642058</v>
       </c>
       <c r="G18">
-        <v>-3.929933207609464</v>
+        <v>-2.934763355231309</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.724364947678639</v>
       </c>
       <c r="E19">
-        <v>-19.56147463715494</v>
+        <v>-20.46579278259069</v>
       </c>
       <c r="F19">
-        <v>-3.231907875598488</v>
+        <v>-3.015014781788688</v>
       </c>
       <c r="G19">
-        <v>-3.079781802579084</v>
+        <v>-2.535604258470304</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.546210243411554</v>
       </c>
       <c r="E20">
-        <v>-19.99818255655865</v>
+        <v>-20.74313011624244</v>
       </c>
       <c r="F20">
-        <v>-2.740933687591818</v>
+        <v>-2.956155964350172</v>
       </c>
       <c r="G20">
-        <v>-3.238654883008708</v>
+        <v>-2.785391540499393</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.420100374848733</v>
       </c>
       <c r="E21">
-        <v>-20.98980515238826</v>
+        <v>-22.07057528753288</v>
       </c>
       <c r="F21">
-        <v>-2.542113085408895</v>
+        <v>-2.725645338805751</v>
       </c>
       <c r="G21">
-        <v>-3.05776667474293</v>
+        <v>-2.461901583129509</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.349106107600006</v>
       </c>
       <c r="E22">
-        <v>-22.99562931544974</v>
+        <v>-22.06081642604635</v>
       </c>
       <c r="F22">
-        <v>-2.436793625449563</v>
+        <v>-2.463139022328198</v>
       </c>
       <c r="G22">
-        <v>-3.557649119536262</v>
+        <v>-1.79534972316157</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.33035876101421</v>
       </c>
       <c r="E23">
-        <v>-22.86977849430257</v>
+        <v>-22.96987588376812</v>
       </c>
       <c r="F23">
-        <v>-2.411065362286013</v>
+        <v>-2.470457648331932</v>
       </c>
       <c r="G23">
-        <v>-2.834390925026146</v>
+        <v>-2.68738283980927</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.351836546622772</v>
       </c>
       <c r="E24">
-        <v>-23.83487328939525</v>
+        <v>-24.0827438426791</v>
       </c>
       <c r="F24">
-        <v>-2.140698667523297</v>
+        <v>-2.073748357294235</v>
       </c>
       <c r="G24">
-        <v>-3.203086381734778</v>
+        <v>-2.392568827900553</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.391439177246047</v>
       </c>
       <c r="E25">
-        <v>-22.54284984179282</v>
+        <v>-24.51008234936093</v>
       </c>
       <c r="F25">
-        <v>-2.332977652326312</v>
+        <v>-2.174289794074219</v>
       </c>
       <c r="G25">
-        <v>-3.555987225675548</v>
+        <v>-2.779776855264789</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.432280251299254</v>
       </c>
       <c r="E26">
-        <v>-24.48499913183244</v>
+        <v>-24.75538978635643</v>
       </c>
       <c r="F26">
-        <v>-1.737492490945443</v>
+        <v>-1.764106278862585</v>
       </c>
       <c r="G26">
-        <v>-3.384732704929049</v>
+        <v>-2.804453661714517</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.451610322797675</v>
       </c>
       <c r="E27">
-        <v>-24.7265615208236</v>
+        <v>-23.6925569367562</v>
       </c>
       <c r="F27">
-        <v>-1.986195721390147</v>
+        <v>-2.029802638208318</v>
       </c>
       <c r="G27">
-        <v>-4.928986329905183</v>
+        <v>-2.85772364998693</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.43548524014132</v>
       </c>
       <c r="E28">
-        <v>-23.97885612046914</v>
+        <v>-24.12230459161011</v>
       </c>
       <c r="F28">
-        <v>-2.141620640442612</v>
+        <v>-2.067819731792399</v>
       </c>
       <c r="G28">
-        <v>-4.130459572014198</v>
+        <v>-2.978085154158212</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.372545520228137</v>
       </c>
       <c r="E29">
-        <v>-24.37711729554771</v>
+        <v>-24.44890719399131</v>
       </c>
       <c r="F29">
-        <v>-2.035140637751959</v>
+        <v>-2.218912289328223</v>
       </c>
       <c r="G29">
-        <v>-3.77346358324135</v>
+        <v>-3.5180483737955</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.255099563205871</v>
       </c>
       <c r="E30">
-        <v>-23.0888298390016</v>
+        <v>-24.02245173974098</v>
       </c>
       <c r="F30">
-        <v>-2.297651924433927</v>
+        <v>-1.83783346281395</v>
       </c>
       <c r="G30">
-        <v>-3.343129079137028</v>
+        <v>-3.409998788484767</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.082886911829855</v>
       </c>
       <c r="E31">
-        <v>-23.55241878011483</v>
+        <v>-23.65036061595273</v>
       </c>
       <c r="F31">
-        <v>-2.470238959337593</v>
+        <v>-2.400534327494223</v>
       </c>
       <c r="G31">
-        <v>-4.462460941965548</v>
+        <v>-3.218225506485866</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.853588342958405</v>
       </c>
       <c r="E32">
-        <v>-23.12447798638998</v>
+        <v>-24.09040149222607</v>
       </c>
       <c r="F32">
-        <v>-2.268281329800268</v>
+        <v>-2.242232488451835</v>
       </c>
       <c r="G32">
-        <v>-4.139345076241602</v>
+        <v>-3.372331401338939</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.573587887898022</v>
       </c>
       <c r="E33">
-        <v>-22.28465889624549</v>
+        <v>-23.96372648880951</v>
       </c>
       <c r="F33">
-        <v>-2.159424741030982</v>
+        <v>-2.068005286090626</v>
       </c>
       <c r="G33">
-        <v>-4.182117324608986</v>
+        <v>-3.231027386086227</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.249633387811349</v>
       </c>
       <c r="E34">
-        <v>-22.85404204712592</v>
+        <v>-22.64033883022995</v>
       </c>
       <c r="F34">
-        <v>-2.20258682455385</v>
+        <v>-2.289187666312122</v>
       </c>
       <c r="G34">
-        <v>-4.181124160947205</v>
+        <v>-2.769110277537258</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.894245371028549</v>
       </c>
       <c r="E35">
-        <v>-22.46366041682069</v>
+        <v>-22.81952601823945</v>
       </c>
       <c r="F35">
-        <v>-2.527055022760806</v>
+        <v>-2.383590072269959</v>
       </c>
       <c r="G35">
-        <v>-3.572424084278029</v>
+        <v>-3.333508633799906</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.525336246630299</v>
       </c>
       <c r="E36">
-        <v>-20.91768920381611</v>
+        <v>-22.09788198579913</v>
       </c>
       <c r="F36">
-        <v>-2.529087007999873</v>
+        <v>-2.30173908919934</v>
       </c>
       <c r="G36">
-        <v>-4.266145591486767</v>
+        <v>-2.415216269934707</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.158228313311226</v>
       </c>
       <c r="E37">
-        <v>-21.14260945082908</v>
+        <v>-21.75028990639237</v>
       </c>
       <c r="F37">
-        <v>-2.073750014029041</v>
+        <v>-2.351552134599285</v>
       </c>
       <c r="G37">
-        <v>-4.008717570353039</v>
+        <v>-3.009042065495937</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.815801442916776</v>
       </c>
       <c r="E38">
-        <v>-19.85209851354521</v>
+        <v>-21.44833578803492</v>
       </c>
       <c r="F38">
-        <v>-2.469936605235571</v>
+        <v>-2.47496645210537</v>
       </c>
       <c r="G38">
-        <v>-3.129771040222078</v>
+        <v>-2.492487713366836</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.5138557583823</v>
       </c>
       <c r="E39">
-        <v>-21.34191664885467</v>
+        <v>-21.20396574515901</v>
       </c>
       <c r="F39">
-        <v>-2.250251084910934</v>
+        <v>-2.710285750423042</v>
       </c>
       <c r="G39">
-        <v>-2.976297459567006</v>
+        <v>-1.997700198158443</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.268181544630091</v>
       </c>
       <c r="E40">
-        <v>-20.41064955459928</v>
+        <v>-20.72388410170984</v>
       </c>
       <c r="F40">
-        <v>-2.366198498648183</v>
+        <v>-2.785800551229648</v>
       </c>
       <c r="G40">
-        <v>-2.575979671867255</v>
+        <v>-2.348445876953146</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.087314668769543</v>
       </c>
       <c r="E41">
-        <v>-19.73526841262132</v>
+        <v>-19.45421320180927</v>
       </c>
       <c r="F41">
-        <v>-2.13368405235639</v>
+        <v>-2.666908291375446</v>
       </c>
       <c r="G41">
-        <v>-2.396614314549542</v>
+        <v>-1.641687441410759</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.972922593552203</v>
       </c>
       <c r="E42">
-        <v>-19.0360040987269</v>
+        <v>-18.69078946817417</v>
       </c>
       <c r="F42">
-        <v>-1.968764386133037</v>
+        <v>-2.741569045389765</v>
       </c>
       <c r="G42">
-        <v>-2.127811258942879</v>
+        <v>-1.697926989031897</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.925130866336451</v>
       </c>
       <c r="E43">
-        <v>-18.00308181994733</v>
+        <v>-19.29645475280405</v>
       </c>
       <c r="F43">
-        <v>-2.706523305679527</v>
+        <v>-2.600848476104394</v>
       </c>
       <c r="G43">
-        <v>-2.668443208779099</v>
+        <v>-1.881711924644537</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.934653885899485</v>
       </c>
       <c r="E44">
-        <v>-18.41064900911167</v>
+        <v>-17.46489985497976</v>
       </c>
       <c r="F44">
-        <v>-2.730218755236607</v>
+        <v>-2.670456188961636</v>
       </c>
       <c r="G44">
-        <v>-2.236999671919121</v>
+        <v>-1.21074710747275</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.993533387362368</v>
       </c>
       <c r="E45">
-        <v>-17.40855205290231</v>
+        <v>-17.48108462108317</v>
       </c>
       <c r="F45">
-        <v>-2.713027646526308</v>
+        <v>-2.911437378477443</v>
       </c>
       <c r="G45">
-        <v>-1.934127792167818</v>
+        <v>-1.189999918578137</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.087116369763548</v>
       </c>
       <c r="E46">
-        <v>-18.15705899315614</v>
+        <v>-16.88348907713496</v>
       </c>
       <c r="F46">
-        <v>-2.658004998530157</v>
+        <v>-2.567790818160874</v>
       </c>
       <c r="G46">
-        <v>-1.915492731327261</v>
+        <v>-0.6000739456621685</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.204339973963082</v>
       </c>
       <c r="E47">
-        <v>-16.58751707294164</v>
+        <v>-16.06278467577684</v>
       </c>
       <c r="F47">
-        <v>-2.847590960906671</v>
+        <v>-2.841236554559797</v>
       </c>
       <c r="G47">
-        <v>-1.81492828948082</v>
+        <v>-0.8306004737437784</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.333696246837428</v>
       </c>
       <c r="E48">
-        <v>-16.14143521234206</v>
+        <v>-16.01466511097134</v>
       </c>
       <c r="F48">
-        <v>-3.005707245650833</v>
+        <v>-2.968693304991542</v>
       </c>
       <c r="G48">
-        <v>-2.605675265354518</v>
+        <v>-1.050063158633144</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.464789456239532</v>
       </c>
       <c r="E49">
-        <v>-15.11431390876632</v>
+        <v>-15.19231234507443</v>
       </c>
       <c r="F49">
-        <v>-3.041341126217059</v>
+        <v>-2.727712115475736</v>
       </c>
       <c r="G49">
-        <v>-2.758347693989087</v>
+        <v>-1.195793373271862</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.593072215445805</v>
       </c>
       <c r="E50">
-        <v>-14.53870863459935</v>
+        <v>-14.38046111040131</v>
       </c>
       <c r="F50">
-        <v>-2.869208036650127</v>
+        <v>-3.290086603399306</v>
       </c>
       <c r="G50">
-        <v>-2.087035269535676</v>
+        <v>-0.8637588978651186</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.713860104241677</v>
       </c>
       <c r="E51">
-        <v>-15.05381349602384</v>
+        <v>-13.6841538900339</v>
       </c>
       <c r="F51">
-        <v>-2.780170966360223</v>
+        <v>-3.026488498684864</v>
       </c>
       <c r="G51">
-        <v>-2.785103523037477</v>
+        <v>-1.032206075994315</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.832524777546407</v>
       </c>
       <c r="E52">
-        <v>-14.08281357082516</v>
+        <v>-13.56241039481169</v>
       </c>
       <c r="F52">
-        <v>-3.338334862775363</v>
+        <v>-3.142754005504789</v>
       </c>
       <c r="G52">
-        <v>-3.522570579002144</v>
+        <v>-0.937107344833211</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.953408698772846</v>
       </c>
       <c r="E53">
-        <v>-14.06390719184313</v>
+        <v>-13.23586666259259</v>
       </c>
       <c r="F53">
-        <v>-3.608127498927939</v>
+        <v>-3.170957430467903</v>
       </c>
       <c r="G53">
-        <v>-1.614511173078881</v>
+        <v>-0.7062332094699777</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.088435463871948</v>
       </c>
       <c r="E54">
-        <v>-13.22277031576241</v>
+        <v>-12.16555277393169</v>
       </c>
       <c r="F54">
-        <v>-3.216862238461441</v>
+        <v>-3.317213979106184</v>
       </c>
       <c r="G54">
-        <v>-2.408515725763222</v>
+        <v>-1.172738734136377</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.247064460286342</v>
       </c>
       <c r="E55">
-        <v>-12.51080816075048</v>
+        <v>-11.80180762773957</v>
       </c>
       <c r="F55">
-        <v>-3.057050285643749</v>
+        <v>-3.460561301425833</v>
       </c>
       <c r="G55">
-        <v>-2.402917593256315</v>
+        <v>-0.9878116603126885</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.436011532295974</v>
       </c>
       <c r="E56">
-        <v>-12.36910768057647</v>
+        <v>-10.94324518367734</v>
       </c>
       <c r="F56">
-        <v>-3.125350006371971</v>
+        <v>-3.431472351709125</v>
       </c>
       <c r="G56">
-        <v>-2.591784216271736</v>
+        <v>-1.073773285785404</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.661397069224303</v>
       </c>
       <c r="E57">
-        <v>-11.95968834554299</v>
+        <v>-11.31796735086404</v>
       </c>
       <c r="F57">
-        <v>-3.262429900922039</v>
+        <v>-3.724416200035142</v>
       </c>
       <c r="G57">
-        <v>-2.792297338494313</v>
+        <v>-0.9660448233919805</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.918472598305791</v>
       </c>
       <c r="E58">
-        <v>-12.38011640088912</v>
+        <v>-9.728735625664191</v>
       </c>
       <c r="F58">
-        <v>-3.190739672414158</v>
+        <v>-3.630835534540882</v>
       </c>
       <c r="G58">
-        <v>-3.007068980354531</v>
+        <v>-0.9859180282642254</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.208332325047287</v>
       </c>
       <c r="E59">
-        <v>-11.21106819343898</v>
+        <v>-10.06497482073372</v>
       </c>
       <c r="F59">
-        <v>-3.55945263033944</v>
+        <v>-3.735219767702454</v>
       </c>
       <c r="G59">
-        <v>-2.855174529921691</v>
+        <v>-1.013961659527392</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.523698201587507</v>
       </c>
       <c r="E60">
-        <v>-10.36629495273009</v>
+        <v>-9.3887966673304</v>
       </c>
       <c r="F60">
-        <v>-3.498102912120706</v>
+        <v>-3.399972024482869</v>
       </c>
       <c r="G60">
-        <v>-2.887720503118266</v>
+        <v>-1.157910800665981</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.861011886251768</v>
       </c>
       <c r="E61">
-        <v>-9.864644187582394</v>
+        <v>-9.079338867542239</v>
       </c>
       <c r="F61">
-        <v>-3.600175171861064</v>
+        <v>-3.535062180531412</v>
       </c>
       <c r="G61">
-        <v>-2.790003130435598</v>
+        <v>-1.569335468649987</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.218349812160762</v>
       </c>
       <c r="E62">
-        <v>-10.28303895809907</v>
+        <v>-8.329690751838481</v>
       </c>
       <c r="F62">
-        <v>-3.569871835531853</v>
+        <v>-3.554132854878662</v>
       </c>
       <c r="G62">
-        <v>-2.707222939226122</v>
+        <v>-1.389076264036671</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.589720547007857</v>
       </c>
       <c r="E63">
-        <v>-10.32394013533635</v>
+        <v>-7.832736014236735</v>
       </c>
       <c r="F63">
-        <v>-3.439444559593668</v>
+        <v>-3.484725606932897</v>
       </c>
       <c r="G63">
-        <v>-3.256200774366845</v>
+        <v>-2.322752733022863</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.9746304629845</v>
       </c>
       <c r="E64">
-        <v>-9.856171412714042</v>
+        <v>-8.119152938273871</v>
       </c>
       <c r="F64">
-        <v>-3.473145859009163</v>
+        <v>-3.742417452065379</v>
       </c>
       <c r="G64">
-        <v>-2.246971035083406</v>
+        <v>-2.106752878767575</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.36288644697116</v>
       </c>
       <c r="E65">
-        <v>-10.21529298694433</v>
+        <v>-8.334481877338595</v>
       </c>
       <c r="F65">
-        <v>-3.536149826931288</v>
+        <v>-3.806428714749308</v>
       </c>
       <c r="G65">
-        <v>-3.761919710945912</v>
+        <v>-2.165114486079387</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.74969851600386</v>
       </c>
       <c r="E66">
-        <v>-9.668126529545532</v>
+        <v>-7.775210808917299</v>
       </c>
       <c r="F66">
-        <v>-3.73677792678712</v>
+        <v>-3.216226880663493</v>
       </c>
       <c r="G66">
-        <v>-3.885598381747544</v>
+        <v>-2.48883287109148</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.12529908676918</v>
       </c>
       <c r="E67">
-        <v>-9.129962678473985</v>
+        <v>-6.941047782808388</v>
       </c>
       <c r="F67">
-        <v>-3.728509991739778</v>
+        <v>-3.813567585026634</v>
       </c>
       <c r="G67">
-        <v>-3.377807043660894</v>
+        <v>-2.220145684578692</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.4773370756051</v>
       </c>
       <c r="E68">
-        <v>-10.11788551103934</v>
+        <v>-7.085075898622344</v>
       </c>
       <c r="F68">
-        <v>-3.449331952913483</v>
+        <v>-3.617824367745111</v>
       </c>
       <c r="G68">
-        <v>-3.693530461195647</v>
+        <v>-2.36128417255444</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.7972608230802</v>
       </c>
       <c r="E69">
-        <v>-8.712392090226702</v>
+        <v>-6.757920822412207</v>
       </c>
       <c r="F69">
-        <v>-3.827607584136683</v>
+        <v>-3.684473152239553</v>
       </c>
       <c r="G69">
-        <v>-3.627524804233659</v>
+        <v>-2.228018161871078</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.07018424377036</v>
       </c>
       <c r="E70">
-        <v>-8.922454414020507</v>
+        <v>-7.03578798752286</v>
       </c>
       <c r="F70">
-        <v>-4.056949383275754</v>
+        <v>-3.594968054367067</v>
       </c>
       <c r="G70">
-        <v>-4.077086956830068</v>
+        <v>-2.555990597901136</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.29118749275179</v>
       </c>
       <c r="E71">
-        <v>-8.699033091904075</v>
+        <v>-6.842376862655259</v>
       </c>
       <c r="F71">
-        <v>-3.712090093081486</v>
+        <v>-3.855852427469937</v>
       </c>
       <c r="G71">
-        <v>-3.716975744704766</v>
+        <v>-2.994409454212358</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.45263344741844</v>
       </c>
       <c r="E72">
-        <v>-8.228578984195217</v>
+        <v>-6.472124299314123</v>
       </c>
       <c r="F72">
-        <v>-3.998667937916989</v>
+        <v>-3.886018254810284</v>
       </c>
       <c r="G72">
-        <v>-3.792512462274317</v>
+        <v>-2.609581709090858</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.54923808429775</v>
       </c>
       <c r="E73">
-        <v>-9.550997549337138</v>
+        <v>-7.550544156448757</v>
       </c>
       <c r="F73">
-        <v>-3.827721070470866</v>
+        <v>-3.934044511722391</v>
       </c>
       <c r="G73">
-        <v>-3.494374662644172</v>
+        <v>-2.418910838756533</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.58113478391815</v>
       </c>
       <c r="E74">
-        <v>-9.50980202128936</v>
+        <v>-7.037739759820166</v>
       </c>
       <c r="F74">
-        <v>-3.815893640693695</v>
+        <v>-3.931006060088922</v>
       </c>
       <c r="G74">
-        <v>-3.672813067210889</v>
+        <v>-2.319614335851634</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.5451783386764</v>
       </c>
       <c r="E75">
-        <v>-8.822701188579545</v>
+        <v>-7.186305406589807</v>
       </c>
       <c r="F75">
-        <v>-3.684281799369507</v>
+        <v>-4.113247717072216</v>
       </c>
       <c r="G75">
-        <v>-3.663801762252992</v>
+        <v>-1.818262008838866</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.44506321584373</v>
       </c>
       <c r="E76">
-        <v>-10.26082679309145</v>
+        <v>-7.699526422827105</v>
       </c>
       <c r="F76">
-        <v>-4.129066220996076</v>
+        <v>-4.358420445646189</v>
       </c>
       <c r="G76">
-        <v>-3.064874416015746</v>
+        <v>-1.488611126220398</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.28369022022051</v>
       </c>
       <c r="E77">
-        <v>-9.369944630036469</v>
+        <v>-8.695297100847746</v>
       </c>
       <c r="F77">
-        <v>-3.898654171172588</v>
+        <v>-4.394254791123893</v>
       </c>
       <c r="G77">
-        <v>-1.639472686444986</v>
+        <v>-1.818685758667892</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.06664869880094</v>
       </c>
       <c r="E78">
-        <v>-10.13481747535402</v>
+        <v>-9.25799622409285</v>
       </c>
       <c r="F78">
-        <v>-4.130997145412001</v>
+        <v>-4.289115915258371</v>
       </c>
       <c r="G78">
-        <v>-2.382557738189797</v>
+        <v>-1.542745166878561</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.80758667212844</v>
       </c>
       <c r="E79">
-        <v>-12.06444100628842</v>
+        <v>-9.10023324661363</v>
       </c>
       <c r="F79">
-        <v>-4.419496802622</v>
+        <v>-4.165982414301836</v>
       </c>
       <c r="G79">
-        <v>-1.815030916392537</v>
+        <v>-0.6698767983577015</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.51602488128186</v>
       </c>
       <c r="E80">
-        <v>-11.35260112007471</v>
+        <v>-9.670254912329137</v>
       </c>
       <c r="F80">
-        <v>-4.460600393148911</v>
+        <v>-4.757240416826219</v>
       </c>
       <c r="G80">
-        <v>-2.662431258079783</v>
+        <v>-1.160231493089011</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.20894876013038</v>
       </c>
       <c r="E81">
-        <v>-11.11875977926662</v>
+        <v>-10.17039316715827</v>
       </c>
       <c r="F81">
-        <v>-4.74459704515729</v>
+        <v>-4.784526010707032</v>
       </c>
       <c r="G81">
-        <v>-2.377704478429225</v>
+        <v>-0.5446752766080045</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.89867426237366</v>
       </c>
       <c r="E82">
-        <v>-12.69777526710517</v>
+        <v>-11.2090167947135</v>
       </c>
       <c r="F82">
-        <v>-4.72751776604637</v>
+        <v>-4.591409546459786</v>
       </c>
       <c r="G82">
-        <v>-2.5657831916063</v>
+        <v>-0.09971809285672134</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.5996523184457</v>
       </c>
       <c r="E83">
-        <v>-12.9987104788109</v>
+        <v>-12.40486903981504</v>
       </c>
       <c r="F83">
-        <v>-4.912076366655294</v>
+        <v>-4.974504619232474</v>
       </c>
       <c r="G83">
-        <v>-1.884181591616834</v>
+        <v>-0.2069069363272438</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.32551429225744</v>
       </c>
       <c r="E84">
-        <v>-13.67995599462879</v>
+        <v>-13.44555765151777</v>
       </c>
       <c r="F84">
-        <v>-4.887811828692492</v>
+        <v>-5.070476781418616</v>
       </c>
       <c r="G84">
-        <v>-1.407913268155124</v>
+        <v>-0.2644640810730127</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.08109857048738</v>
       </c>
       <c r="E85">
-        <v>-15.40217994448591</v>
+        <v>-14.26129884536348</v>
       </c>
       <c r="F85">
-        <v>-5.13614063707113</v>
+        <v>-5.150607245393621</v>
       </c>
       <c r="G85">
-        <v>-1.157943906121374</v>
+        <v>-0.160714894417793</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.875744444267879</v>
       </c>
       <c r="E86">
-        <v>-16.07382509540754</v>
+        <v>-15.84539528103863</v>
       </c>
       <c r="F86">
-        <v>-4.905022818220456</v>
+        <v>-5.371249530068491</v>
       </c>
       <c r="G86">
-        <v>-1.263143111722795</v>
+        <v>0.3137524922705536</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.7091826892522</v>
       </c>
       <c r="E87">
-        <v>-17.61036349705414</v>
+        <v>-16.54885296186415</v>
       </c>
       <c r="F87">
-        <v>-5.108207259881328</v>
+        <v>-5.474267785382846</v>
       </c>
       <c r="G87">
-        <v>-1.166564566705636</v>
+        <v>0.2588040574097304</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.5836539641607</v>
       </c>
       <c r="E88">
-        <v>-19.12415084528621</v>
+        <v>-18.23537442264479</v>
       </c>
       <c r="F88">
-        <v>-5.381860916498353</v>
+        <v>-5.409188757116708</v>
       </c>
       <c r="G88">
-        <v>-1.037314247761411</v>
+        <v>0.6255032551581819</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.497970331472528</v>
       </c>
       <c r="E89">
-        <v>-21.03596841642245</v>
+        <v>-19.64129352001414</v>
       </c>
       <c r="F89">
-        <v>-5.620694149338701</v>
+        <v>-5.660801213880045</v>
       </c>
       <c r="G89">
-        <v>-1.567839102066236</v>
+        <v>0.4160649021617296</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.44690757656636</v>
       </c>
       <c r="E90">
-        <v>-22.12555549046</v>
+        <v>-21.30264572226015</v>
       </c>
       <c r="F90">
-        <v>-5.629440052377458</v>
+        <v>-5.698993092986115</v>
       </c>
       <c r="G90">
-        <v>-1.711457188650899</v>
+        <v>0.6623694902835059</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.431301006655504</v>
       </c>
       <c r="E91">
-        <v>-24.90011528716757</v>
+        <v>-23.21804984481048</v>
       </c>
       <c r="F91">
-        <v>-5.202964207087564</v>
+        <v>-5.607148685568124</v>
       </c>
       <c r="G91">
-        <v>-1.258087908684328</v>
+        <v>-0.05507869680518866</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.44427814922369</v>
       </c>
       <c r="E92">
-        <v>-25.99300814723072</v>
+        <v>-25.32825533374875</v>
       </c>
       <c r="F92">
-        <v>-5.567224690222798</v>
+        <v>-5.736202528352466</v>
       </c>
       <c r="G92">
-        <v>-1.638906583157771</v>
+        <v>0.09976213915760331</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.484319100009269</v>
       </c>
       <c r="E93">
-        <v>-28.06510652739445</v>
+        <v>-27.87812583561774</v>
       </c>
       <c r="F93">
-        <v>-5.521631348372714</v>
+        <v>-5.667508504740512</v>
       </c>
       <c r="G93">
-        <v>-2.053300810490502</v>
+        <v>-0.1647736232489394</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.54256829127136</v>
       </c>
       <c r="E94">
-        <v>-30.77783454000129</v>
+        <v>-29.97440853121944</v>
       </c>
       <c r="F94">
-        <v>-5.745138127526465</v>
+        <v>-5.841658668933261</v>
       </c>
       <c r="G94">
-        <v>-2.390407041663409</v>
+        <v>-0.2658776840182815</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.614172558354607</v>
       </c>
       <c r="E95">
-        <v>-32.63636555748928</v>
+        <v>-31.77000055271182</v>
       </c>
       <c r="F95">
-        <v>-5.716082312505869</v>
+        <v>-5.932580275064534</v>
       </c>
       <c r="G95">
-        <v>-2.732492333327379</v>
+        <v>-0.5769530956158986</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.691663864447632</v>
       </c>
       <c r="E96">
-        <v>-34.24115032666847</v>
+        <v>-34.55895636828977</v>
       </c>
       <c r="F96">
-        <v>-5.714545690973677</v>
+        <v>-5.866932986760077</v>
       </c>
       <c r="G96">
-        <v>-3.349299936022229</v>
+        <v>-1.19752809913444</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.765670317875648</v>
       </c>
       <c r="E97">
-        <v>-37.24834915433508</v>
+        <v>-37.1755629916098</v>
       </c>
       <c r="F97">
-        <v>-5.987520086320406</v>
+        <v>-6.078132711410436</v>
       </c>
       <c r="G97">
-        <v>-3.249377740010407</v>
+        <v>-1.296649143125758</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.83063007491565</v>
       </c>
       <c r="E98">
-        <v>-39.67500893540338</v>
+        <v>-39.5781403479053</v>
       </c>
       <c r="F98">
-        <v>-5.799696061409646</v>
+        <v>-5.914486245885184</v>
       </c>
       <c r="G98">
-        <v>-3.889700147670701</v>
+        <v>-2.416037285228446</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.878842733657564</v>
       </c>
       <c r="E99">
-        <v>-43.0072820054736</v>
+        <v>-42.49214091625705</v>
       </c>
       <c r="F99">
-        <v>-6.40818162081005</v>
+        <v>-6.350007034846247</v>
       </c>
       <c r="G99">
-        <v>-4.175406848800883</v>
+        <v>-2.522924869054895</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.9039152071839</v>
       </c>
       <c r="E100">
-        <v>-45.02356015078178</v>
+        <v>-44.64992708159392</v>
       </c>
       <c r="F100">
-        <v>-5.820683577926975</v>
+        <v>-6.081128916306361</v>
       </c>
       <c r="G100">
-        <v>-4.67939768060845</v>
+        <v>-3.429497901711074</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.90506114036102</v>
       </c>
       <c r="E101">
-        <v>-47.74348843706082</v>
+        <v>-47.89019967372432</v>
       </c>
       <c r="F101">
-        <v>-6.146028188846091</v>
+        <v>-6.399006623456644</v>
       </c>
       <c r="G101">
-        <v>-5.805456571972769</v>
+        <v>-3.945525877099431</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.869739053812562</v>
       </c>
       <c r="E102">
-        <v>-49.81265576242308</v>
+        <v>-49.58547014628778</v>
       </c>
       <c r="F102">
-        <v>-5.848518379395843</v>
+        <v>-6.193739666145134</v>
       </c>
       <c r="G102">
-        <v>-6.088776369769136</v>
+        <v>-4.260696433529127</v>
       </c>
     </row>
   </sheetData>
